--- a/outputs/etf_trend_strategy/threshold_0.7/backtests/window_40/return_vol_r2/post_rank_positive_return/rebalance_1d/next_day_vwap/next_day_vwap_annual_metrics.xlsx
+++ b/outputs/etf_trend_strategy/threshold_0.7/backtests/window_40/return_vol_r2/post_rank_positive_return/rebalance_1d/next_day_vwap/next_day_vwap_annual_metrics.xlsx
@@ -466,10 +466,10 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
@@ -524,25 +524,25 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.1463470166086718</v>
+        <v>-0.03477207225515455</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.2889416731591149</v>
+        <v>0.1786027907570343</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>0.6271454182191816</v>
+        <v>-0.2181970070011978</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.8862648883757132</v>
+        <v>-0.2992201179050442</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.1905741153697719</v>
+        <v>0.1524908295719816</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.8757214484171059</v>
+        <v>-0.2570924954540811</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>37.7666892571909</v>
+        <v>38.26478539105206</v>
       </c>
     </row>
     <row r="3">
@@ -552,25 +552,25 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-0.3287607241273128</v>
+        <v>-0.03389782966949606</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.2436655847251419</v>
+        <v>0.291245350160425</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>-1.641419177656522</v>
+        <v>-0.02984780581029322</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-2.105210385369369</v>
+        <v>-0.04354500860170842</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.3636929925724113</v>
+        <v>0.1865281638259718</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-0.9341038086261814</v>
+        <v>-0.1891058775003361</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>53.15809030125638</v>
+        <v>23.76978520620641</v>
       </c>
     </row>
     <row r="4">
@@ -580,25 +580,25 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0.04832433687167614</v>
+        <v>-0.05333207681299457</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.2193998853906328</v>
+        <v>0.2198540329601791</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>0.2649164072580171</v>
+        <v>-0.2177766504735355</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.4074666801419435</v>
+        <v>-0.3047382418156197</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.2060536748480171</v>
+        <v>0.2636537514761019</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0.2444542416326079</v>
+        <v>-0.2104032851666207</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>44.44311934280514</v>
+        <v>57.38710281349771</v>
       </c>
     </row>
     <row r="5">
@@ -608,25 +608,25 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0.04651470288989423</v>
+        <v>-0.03434432850765845</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0.2195235940456178</v>
+        <v>0.2569963087784074</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.2568383173182369</v>
+        <v>-0.07151504878864223</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.3769765221401312</v>
+        <v>-0.1006412242516173</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.1677256703000604</v>
+        <v>0.186669437018942</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.289059339818995</v>
+        <v>-0.1914499520916328</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>41.63784224163858</v>
+        <v>41.71596231242248</v>
       </c>
     </row>
     <row r="6">
@@ -636,25 +636,25 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.09597987135738628</v>
+        <v>0.1032452867346376</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0.2474479405973622</v>
+        <v>0.2603145572384551</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.4483981847117089</v>
+        <v>0.4647997320265368</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.6068437377214825</v>
+        <v>0.6407821235840655</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.2667563682998072</v>
+        <v>0.243469750737475</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.3737732225872701</v>
+        <v>0.4405780867990073</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>56.52411609476474</v>
+        <v>49.34766875401608</v>
       </c>
     </row>
     <row r="7">
@@ -664,25 +664,25 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>-0.01327585352501215</v>
+        <v>0.2740812966465678</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.3298438087643883</v>
+        <v>0.3771988285001858</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.04607453099858262</v>
+        <v>1.312604897616496</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.06283173965639356</v>
+        <v>1.983318894082164</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.2367070911477266</v>
+        <v>0.1234609404893311</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.1011311711024471</v>
+        <v>4.465996886612368</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>34.77414338557124</v>
+        <v>39.06952177065499</v>
       </c>
     </row>
   </sheetData>
